--- a/data/S1986_87_FINAL.xlsx
+++ b/data/S1986_87_FINAL.xlsx
@@ -27,8 +27,11 @@
     <sheet name="SERIES" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="CLUBS" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="META" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -36,7 +39,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,8 +54,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +81,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -87,12 +99,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -22360,7 +22378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22404,6 +22422,57 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0023</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1986_87_0023 'Kvalifikace o 2. ČNHL sk. A' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0024</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1986_87_0024 'Kvalifikace o 2. ČNHL sk. B' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0025</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1986_87_0025 'Kvalifikace o 2. ČNHL sk. C' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -57277,6 +57346,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0023</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1986_87_0023 'Kvalifikace o 2. ČNHL sk. A' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0024</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1986_87_0024 'Kvalifikace o 2. ČNHL sk. B' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0025</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1986_87_0025 'Kvalifikace o 2. ČNHL sk. C' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1986_87_FINAL.xlsx
+++ b/data/S1986_87_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$58</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -5632,6 +5632,11 @@
           <t>CLUB_S1985_86_0302</t>
         </is>
       </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>zanik</t>
+        </is>
+      </c>
       <c r="V42" t="inlineStr">
         <is>
           <t>TR_S1986_87_00257</t>
@@ -22378,7 +22383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22426,14 +22431,9 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NODE_S1986_87_0023</t>
-        </is>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1986_87_0023 'Kvalifikace o 2. ČNHL sk. A' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22443,14 +22443,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1986_87_0024</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1986_87_0024 'Kvalifikace o 2. ČNHL sk. B' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22460,17 +22455,660 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1986_87_0025</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1986_87_0025 'Kvalifikace o 2. ČNHL sk. C' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -32340,12 +32978,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -32864,12 +33502,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -32906,12 +33544,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -33074,12 +33712,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -33116,12 +33754,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -33200,12 +33838,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -33242,12 +33880,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -34314,12 +34952,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34529,12 +35167,12 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -34828,12 +35466,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor.</t>
+          <t>Vodní stavby Tábor = HC Tábor (Wiki D42 - registr ustavy 04/2026). Chain DSK Tábor (1921) -&gt; ČSSZ -&gt; DSO Tatran -&gt; Vodni stavby. city Tábor. || TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Vodní stavby Tábor</t>
+          <t>Tábor</t>
         </is>
       </c>
     </row>
@@ -34954,12 +35592,12 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -35085,12 +35723,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -35421,12 +36059,12 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky.</t>
+          <t>Nové Zámky = TJ Lokomotiva Nové Zámky (Wiki D42 - registr ustavy 04/2026). Slovensky/Nitriansky kraj. Železničárský klub. Patterns: Lokomotíva Nové Zámky -&gt; Lokomotiva Nové Zámky. city Nové Zámky. || TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Lokomotiva Nové Zámky</t>
+          <t>Nové Zámky</t>
         </is>
       </c>
     </row>
@@ -35594,12 +36232,12 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -36753,12 +37391,12 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -38751,12 +39389,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -38961,12 +39599,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -39097,12 +39735,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -39149,12 +39787,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -39468,12 +40106,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -39656,12 +40294,12 @@
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -40072,19 +40710,14 @@
           <t>Soutěž</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0155</t>
-        </is>
-      </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40220,12 +40853,12 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40260,19 +40893,14 @@
           <t>Soutěž</t>
         </is>
       </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0155</t>
-        </is>
-      </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -40307,19 +40935,14 @@
           <t>Soutěž</t>
         </is>
       </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0155</t>
-        </is>
-      </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach] || TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -42708,12 +43331,12 @@
       </c>
       <c r="I241" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J241" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -43912,12 +44535,12 @@
       </c>
       <c r="I268" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J268" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -44038,12 +44661,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou.</t>
+          <t>Jablonec nad Nisou = TJ Bižuterie Jablonec (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Bižuterie Jablonec** = sklarsky podnik (svetove znamy vyrobce bizutérie). city Jablonec nad Nisou. || TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Bižuterie Jablonec</t>
+          <t>Jablonec nad Nisou</t>
         </is>
       </c>
     </row>
@@ -44085,12 +44708,12 @@
       </c>
       <c r="I272" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J272" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44132,12 +44755,12 @@
       </c>
       <c r="I273" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J273" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -44231,12 +44854,12 @@
       </c>
       <c r="I275" t="inlineStr">
         <is>
-          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou.</t>
+          <t>Hrádek nL Nisou = TJ ČSAD Hrádek nL Nisou (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Liberec). **ČSAD** = Československá státní automobilová doprava. **Hrádek nL Nisou** = pohranicni mesto trojmezi (CR-DDR/Polsko-NSR). city Hrádek nad Nisou. || TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J275" t="inlineStr">
         <is>
-          <t>ČSAD Hrádek nad Nisou</t>
+          <t>Hrádek nad Nisou</t>
         </is>
       </c>
     </row>
@@ -44278,12 +44901,12 @@
       </c>
       <c r="I276" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J276" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44330,12 +44953,12 @@
       </c>
       <c r="I277" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J277" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44476,12 +45099,12 @@
       </c>
       <c r="I280" t="inlineStr">
         <is>
-          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor.</t>
+          <t>Nový Bor = TJ Crystalex 08 Nový Bor (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj (okres Ceska Lipa). **Crystalex** = svetove znama sklarna (drive Crystalex Nový Bor, dnes pod Crystalex CZ). **Nový Bor = sklarsky mesto**. city Nový Bor. || TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J280" t="inlineStr">
         <is>
-          <t>Crystalex 08 Nový Bor</t>
+          <t>Nový Bor</t>
         </is>
       </c>
     </row>
@@ -44617,12 +45240,12 @@
       </c>
       <c r="I283" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J283" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44664,12 +45287,12 @@
       </c>
       <c r="I284" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J284" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44805,12 +45428,12 @@
       </c>
       <c r="I287" t="inlineStr">
         <is>
-          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa.</t>
+          <t>Česká Lípa = TJ Akumulátory Česká Lípa (Wiki D42 - registr ustavy 04/2026). Severocesky/Liberecky kraj. **Akumulátory** = vyrobce automobilovych akumulátorů (drive Pal/Magneton Česká Lípa). city Česká Lípa. || TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J287" t="inlineStr">
         <is>
-          <t>Akumulátory Česká Lípa</t>
+          <t>Česká Lípa</t>
         </is>
       </c>
     </row>
@@ -44847,12 +45470,12 @@
       </c>
       <c r="I288" t="inlineStr">
         <is>
-          <t>Dolní Poustevna = TJ Centroflor Dolní Poustevna (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Pustevna' = preklep z 'Poustevna'. Severocesky/Ustecky kraj (okres Decin). city Dolní Poustevna.</t>
+          <t>Dolní Poustevna = TJ Centroflor Dolní Poustevna (Wiki D42 - registr ustavy 04/2026). PARSING CHYBA: 'Pustevna' = preklep z 'Poustevna'. Severocesky/Ustecky kraj (okres Decin). city Dolní Poustevna. || TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J288" t="inlineStr">
         <is>
-          <t>Centroflor Dolní Pustevna</t>
+          <t>Dolní Pustevna</t>
         </is>
       </c>
     </row>
@@ -45077,12 +45700,12 @@
       </c>
       <c r="I293" t="inlineStr">
         <is>
-          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří.</t>
+          <t>Klášterec nad Ohří = Sokol Klášterec (Wiki D42 - registr ustavy 04/2026). Severocesky kraj (okres Chomutov). HC Klášterec dnes mensi soutez. city Klášterec nad Ohří. || TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J293" t="inlineStr">
         <is>
-          <t>Klášterec</t>
+          <t>Klášterec nad Ohří</t>
         </is>
       </c>
     </row>
@@ -45705,12 +46328,12 @@
       </c>
       <c r="I307" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J307" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -47950,12 +48573,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -48370,12 +48993,12 @@
       </c>
       <c r="I367" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J367" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -49687,12 +50310,12 @@
       </c>
       <c r="I398" t="inlineStr">
         <is>
-          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška.</t>
+          <t>Veverská Bítýška = TJ RICO Veverská Bítýška (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Brno-venkov). **RICO** = pojmenovani po vyrobci (rychlosvyrabne ucely?). NE Veverí (mestska cast Brna), NE Bystřice u Veveří. city Veverská Bítýška. || TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J398" t="inlineStr">
         <is>
-          <t>RICO Veverská Bítýška</t>
+          <t>Veverská Bítýška</t>
         </is>
       </c>
     </row>
@@ -50216,12 +50839,12 @@
       </c>
       <c r="I410" t="inlineStr">
         <is>
-          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště.</t>
+          <t>Uherské Hradiště = TJ Slovácká Slavia Uherské Hradiště (Wiki D42 - registr ustavy 04/2026). Zlinsky/Severomoravsky kraj. **Slovácká** = Moravske Slovacko region. city Uherské Hradiště. || TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J410" t="inlineStr">
         <is>
-          <t>Slovácká Slavia Uherské Hradiště</t>
+          <t>Uherské Hradiště</t>
         </is>
       </c>
     </row>
@@ -50965,12 +51588,12 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -51091,12 +51714,12 @@
       </c>
       <c r="I430" t="inlineStr">
         <is>
-          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek.</t>
+          <t>Frýdek-Místek = TJ Slezan Frýdek-Místek (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **Slezan** = textilni podnik. Patterns: TJ Slezan Frýdek-Místek (z 80/81). city Frýdek-Místek. || TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J430" t="inlineStr">
         <is>
-          <t>Slezan Frýdek Místek</t>
+          <t>Frýdek Místek</t>
         </is>
       </c>
     </row>
@@ -53780,12 +54403,12 @@
       </c>
       <c r="I492" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J492" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -57352,11 +57975,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -57401,21 +58024,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>NODE_S1986_87_0023</t>
+          <t>CLUB_S1986_87_0006</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1986_87_0023 'Kvalifikace o 2. ČNHL sk. A' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -57423,21 +58044,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1986_87_0024</t>
+          <t>CLUB_S1986_87_0018</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1986_87_0024 'Kvalifikace o 2. ČNHL sk. B' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -57445,24 +58064,1102 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1986_87_0025</t>
+          <t>CLUB_S1986_87_0019</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1986_87_0025 'Kvalifikace o 2. ČNHL sk. C' (L35, parent=NODE_S1986_87_0022) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0023</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0024</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0026</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0027</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0061</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0066</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0073</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0076</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0079</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0087</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0091</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0118</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0163</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0168</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0168</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0171</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0172</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0179</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0183</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0192</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0192</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0195</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0196</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0196</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0197</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0197</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0249</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0277</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0280</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0281</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0282</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0284</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0285</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0286</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0289</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0292</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0293</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0296</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0297</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0302</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0314</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0317</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0336</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0367</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0368</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0372</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0378</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0384</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0402</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0411</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0423</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>55</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0442</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>56</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0445</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>CLUB_S1986_87_0509</t>
+        </is>
+      </c>
+      <c r="D58" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F58"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -73540,11 +75237,7 @@
           <t>CLUB_S1986_87_0192</t>
         </is>
       </c>
-      <c r="R51" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0155</t>
-        </is>
-      </c>
+      <c r="R51" s="3" t="n"/>
       <c r="S51" s="3" t="n"/>
       <c r="T51" s="3" t="n"/>
       <c r="U51" s="3" t="n"/>
@@ -73732,11 +75425,7 @@
           <t>CLUB_S1986_87_0196</t>
         </is>
       </c>
-      <c r="R55" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0155</t>
-        </is>
-      </c>
+      <c r="R55" s="3" t="n"/>
       <c r="S55" s="3" t="n"/>
       <c r="T55" s="3" t="n"/>
       <c r="U55" s="3" t="n"/>
@@ -73781,11 +75470,7 @@
           <t>CLUB_S1986_87_0197</t>
         </is>
       </c>
-      <c r="R56" s="3" t="inlineStr">
-        <is>
-          <t>CLUB_S1985_86_0155</t>
-        </is>
-      </c>
+      <c r="R56" s="3" t="n"/>
       <c r="S56" s="3" t="n"/>
       <c r="T56" s="3" t="n"/>
       <c r="U56" s="3" t="n"/>

--- a/data/S1986_87_FINAL.xlsx
+++ b/data/S1986_87_FINAL.xlsx
@@ -30,7 +30,7 @@
     <sheet name="TODO" sheetId="21" state="visible" r:id="rId21"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$58</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="20" hidden="1">'TODO'!$A$1:$F$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -22383,7 +22383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D59"/>
+  <dimension ref="A1:D49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22433,7 +22433,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -22445,7 +22445,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22457,7 +22457,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22469,7 +22469,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22481,7 +22481,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22493,7 +22493,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22505,7 +22505,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22517,7 +22517,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22529,7 +22529,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22541,7 +22541,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -22553,7 +22553,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22565,7 +22565,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22577,7 +22577,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22589,7 +22589,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22601,7 +22601,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22613,7 +22613,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -22625,7 +22625,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -22637,7 +22637,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -22649,7 +22649,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -22661,7 +22661,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -22673,7 +22673,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -22685,7 +22685,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -22697,7 +22697,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -22709,7 +22709,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -22721,7 +22721,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -22733,7 +22733,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -22745,7 +22745,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -22757,7 +22757,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -22769,7 +22769,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -22781,7 +22781,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -22793,7 +22793,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22805,7 +22805,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -22829,7 +22829,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -22841,7 +22841,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22853,7 +22853,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -22865,7 +22865,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22877,7 +22877,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22889,7 +22889,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -22901,7 +22901,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -22913,7 +22913,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -22925,7 +22925,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22937,7 +22937,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -22949,7 +22949,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -22961,7 +22961,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22973,7 +22973,7 @@
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -22985,130 +22985,10 @@
     <row r="49">
       <c r="C49" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -23125,7 +23005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K131"/>
+  <dimension ref="A1:L131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23184,6 +23064,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -23226,6 +23111,11 @@
           <t>12 týmů: základ + playoff (QF/SF/finále/o místo) + o udržení. Mistr: Tesla Pardubice.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -23273,6 +23163,11 @@
           <t>Série TJ Plastika Nitra – TJ Poldi SONP Kladno 0:3. V kvalifikaci je 1. a 3. utkání hráno doma. Případné 5. utkání se mělo hrát v Gottwaldově.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -23315,6 +23210,11 @@
           <t>I.ČNHL: základní část + čtvrtfinále + semifinále + O 3.místo + finále + O 5.-8.místo + o udržení. I.SNHL (12). Kvalifikace o 1. CHL.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -23362,6 +23262,11 @@
           <t>V play-off je 1. a 3. utkání hráno doma. ASD Dukla Jihlava "B" hrála svá domácí utkání v Písku.</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -23446,6 +23351,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -23488,6 +23398,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -23530,6 +23445,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -23572,6 +23492,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -23614,6 +23539,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -23656,6 +23586,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -23698,6 +23633,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -23740,6 +23680,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -23782,6 +23727,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -24338,6 +24288,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0020</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -24506,6 +24461,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0024</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -24548,6 +24508,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0025</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -24590,6 +24555,11 @@
           <t>II.ČNHL: 3 skupiny + finále.</t>
         </is>
       </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0026</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -24632,6 +24602,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0027</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -24674,6 +24649,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0028</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -24716,6 +24696,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0029</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -24758,6 +24743,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0030</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -24800,6 +24790,11 @@
           <t>II.SNHL: červená+modrá sk. + fáze.</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0031</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -24842,6 +24837,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0032</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -24884,6 +24884,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0033</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -24926,6 +24931,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0034</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -24968,6 +24978,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0035</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -25010,6 +25025,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0036</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -25052,6 +25072,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0037</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -25099,6 +25124,11 @@
           <t>Ve finále je první utkání hráno doma. Do kvalifikace o 2. SNHL sestoupila Levoča. Přímo do krajského přeboru sestoupil TJ Spartak BEZ Bratislava.</t>
         </is>
       </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0038</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -25141,6 +25171,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0039</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -25183,6 +25218,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0040</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -25225,6 +25265,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0041</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -25398,6 +25443,11 @@
           <t>kvalifikace o KP II.třídy</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0045</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -25524,6 +25574,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0049</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -25566,6 +25621,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0050</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -25608,6 +25668,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0051</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -25650,6 +25715,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0052</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -25692,6 +25762,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0053</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -25734,6 +25809,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0054</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -25781,6 +25861,11 @@
           <t>Kvalifikace o KP</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0055</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -25823,6 +25908,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0056</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -25865,6 +25955,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0057</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -26033,6 +26128,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0058</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -26075,6 +26175,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0059</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -26117,6 +26222,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0060</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -26206,6 +26316,11 @@
           <t>kvalifikace o I.třídu</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0062</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -26248,6 +26363,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0063</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -26290,6 +26410,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0064</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -26458,6 +26583,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0065</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -26500,6 +26630,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0066</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -26542,6 +26677,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0067</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -26584,6 +26724,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0068</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -27088,6 +27233,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0071</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -27130,6 +27280,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0072</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -27256,6 +27411,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0075</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -27424,6 +27584,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0079</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -27466,6 +27631,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0080</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -27508,6 +27678,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0081</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -27891,6 +28066,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0082</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -27933,6 +28113,11 @@
           <t>Kontejner L50</t>
         </is>
       </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0083</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -27975,6 +28160,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0084</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -28059,6 +28249,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0086</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -28101,6 +28296,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0087</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -28148,6 +28348,11 @@
           <t>kvalifikace o KS</t>
         </is>
       </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0088</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -28274,6 +28479,11 @@
           <t>Kontejner slovenských krajských větví.</t>
         </is>
       </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0091</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -28358,6 +28568,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0093</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -28398,6 +28613,11 @@
       <c r="J124" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>NODE_S1985_86_0094</t>
         </is>
       </c>
     </row>
@@ -32978,12 +33198,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -33544,12 +33764,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -33754,12 +33974,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -33838,12 +34058,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -39599,12 +39819,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -39735,12 +39955,12 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -39787,12 +40007,12 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -40106,12 +40326,12 @@
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -48573,12 +48793,12 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J357" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -51588,12 +51808,12 @@
       </c>
       <c r="I427" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J427" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -57975,7 +58195,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -58029,12 +58249,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0006</t>
+          <t>CLUB_S1986_87_0018</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58049,12 +58269,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0018</t>
+          <t>CLUB_S1986_87_0023</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58069,12 +58289,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0019</t>
+          <t>CLUB_S1986_87_0027</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58089,12 +58309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0023</t>
+          <t>CLUB_S1986_87_0061</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58109,12 +58329,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0024</t>
+          <t>CLUB_S1986_87_0066</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58129,12 +58349,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0026</t>
+          <t>CLUB_S1986_87_0073</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58149,12 +58369,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0027</t>
+          <t>CLUB_S1986_87_0076</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58169,12 +58389,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0061</t>
+          <t>CLUB_S1986_87_0079</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58189,12 +58409,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0066</t>
+          <t>CLUB_S1986_87_0087</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58209,12 +58429,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0073</t>
+          <t>CLUB_S1986_87_0091</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58229,12 +58449,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0076</t>
+          <t>CLUB_S1986_87_0118</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58249,12 +58469,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0079</t>
+          <t>CLUB_S1986_87_0163</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58269,12 +58489,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0087</t>
+          <t>CLUB_S1986_87_0168</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58289,12 +58509,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0091</t>
+          <t>CLUB_S1986_87_0183</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58309,12 +58529,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0118</t>
+          <t>CLUB_S1986_87_0192</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58329,12 +58549,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0163</t>
+          <t>CLUB_S1986_87_0192</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58349,12 +58569,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0168</t>
+          <t>CLUB_S1986_87_0195</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58369,12 +58589,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0168</t>
+          <t>CLUB_S1986_87_0196</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58389,12 +58609,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0171</t>
+          <t>CLUB_S1986_87_0196</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58409,12 +58629,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0172</t>
+          <t>CLUB_S1986_87_0197</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58429,12 +58649,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0179</t>
+          <t>CLUB_S1986_87_0197</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58449,12 +58669,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0183</t>
+          <t>CLUB_S1986_87_0249</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58469,12 +58689,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0192</t>
+          <t>CLUB_S1986_87_0277</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58489,12 +58709,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0192</t>
+          <t>CLUB_S1986_87_0280</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58509,12 +58729,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0195</t>
+          <t>CLUB_S1986_87_0281</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58529,12 +58749,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0196</t>
+          <t>CLUB_S1986_87_0282</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58549,12 +58769,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0196</t>
+          <t>CLUB_S1986_87_0284</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58569,12 +58789,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0197</t>
+          <t>CLUB_S1986_87_0285</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58589,12 +58809,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0197</t>
+          <t>CLUB_S1986_87_0286</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58609,12 +58829,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0249</t>
+          <t>CLUB_S1986_87_0289</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58629,12 +58849,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0277</t>
+          <t>CLUB_S1986_87_0292</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58649,12 +58869,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0280</t>
+          <t>CLUB_S1986_87_0293</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58669,7 +58889,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0281</t>
+          <t>CLUB_S1986_87_0296</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
@@ -58689,12 +58909,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0282</t>
+          <t>CLUB_S1986_87_0297</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58709,12 +58929,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0284</t>
+          <t>CLUB_S1986_87_0302</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58729,12 +58949,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0285</t>
+          <t>CLUB_S1986_87_0314</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -58749,12 +58969,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0286</t>
+          <t>CLUB_S1986_87_0317</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58769,12 +58989,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0289</t>
+          <t>CLUB_S1986_87_0336</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -58789,12 +59009,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0292</t>
+          <t>CLUB_S1986_87_0367</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
     </row>
@@ -58809,12 +59029,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0293</t>
+          <t>CLUB_S1986_87_0372</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -58829,12 +59049,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0296</t>
+          <t>CLUB_S1986_87_0378</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58849,12 +59069,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0297</t>
+          <t>CLUB_S1986_87_0384</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -58869,12 +59089,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0302</t>
+          <t>CLUB_S1986_87_0402</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -58889,12 +59109,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0314</t>
+          <t>CLUB_S1986_87_0411</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58909,12 +59129,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0317</t>
+          <t>CLUB_S1986_87_0423</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58929,12 +59149,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0336</t>
+          <t>CLUB_S1986_87_0445</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -58949,217 +59169,17 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CLUB_S1986_87_0367</t>
+          <t>CLUB_S1986_87_0509</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0368</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0372</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0378</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0384</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0402</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0411</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0423</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>55</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0442</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>56</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0445</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>CLUB_S1986_87_0509</t>
-        </is>
-      </c>
-      <c r="D58" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F58"/>
+  <autoFilter ref="A1:F48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1986_87_FINAL.xlsx
+++ b/data/S1986_87_FINAL.xlsx
@@ -22383,7 +22383,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22431,21 +22431,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30JHCK</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] TJ Sokol Kluky — odstoupily</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -22457,7 +22462,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -22469,7 +22474,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -22481,7 +22486,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -22493,7 +22498,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -22505,7 +22510,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vodní stavby Tábor' → 'Tábor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -22517,7 +22522,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -22529,7 +22534,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -22541,7 +22546,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva Nové Zámky' → 'Nové Zámky' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -22553,7 +22558,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -22565,7 +22570,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -22577,7 +22582,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -22589,7 +22594,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -22601,7 +22606,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -22613,7 +22618,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -22625,7 +22630,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -22649,7 +22654,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -22661,7 +22666,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -22673,7 +22678,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -22685,7 +22690,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id vymazáno (hub-link, nejisté pokračování) [polish_almanach]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -22697,7 +22702,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -22709,7 +22714,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -22721,7 +22726,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Bižuterie Jablonec' → 'Jablonec nad Nisou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -22733,7 +22738,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -22745,7 +22750,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -22757,7 +22762,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'ČSAD Hrádek nad Nisou' → 'Hrádek nad Nisou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -22781,7 +22786,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -22793,7 +22798,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Crystalex 08 Nový Bor' → 'Nový Bor' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -22829,7 +22834,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Akumulátory Česká Lípa' → 'Česká Lípa' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -22841,7 +22846,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Centroflor Dolní Pustevna' → 'Dolní Pustevna' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -22853,7 +22858,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Klášterec' → 'Klášterec nad Ohří' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -22865,7 +22870,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -22877,7 +22882,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -22889,7 +22894,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -22901,7 +22906,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: Smart fix prev → 52/53 0313 (MEZ Třebíč A). Identity transition MEZ → Spartak (D28) předpoklad. K vyřešení složitější situace v Třebíči.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -22913,7 +22918,7 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -22925,7 +22930,7 @@
     <row r="44">
       <c r="C44" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -22937,7 +22942,7 @@
     <row r="45">
       <c r="C45" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -22949,7 +22954,7 @@
     <row r="46">
       <c r="C46" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -22961,7 +22966,7 @@
     <row r="47">
       <c r="C47" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'RICO Veverská Bítýška' → 'Veverská Bítýška' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -22973,7 +22978,7 @@
     <row r="48">
       <c r="C48" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slovácká Slavia Uherské Hradiště' → 'Uherské Hradiště' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -22985,10 +22990,22 @@
     <row r="49">
       <c r="C49" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Slezan Frýdek Místek' → 'Frýdek Místek' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -73297,7 +73314,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / Základní část / TJ Sokol Kluky — odstoupily</t>
+          <t>Krajský přebor / Základní část</t>
         </is>
       </c>
       <c r="C13" s="2" t="n"/>

--- a/data/S1986_87_FINAL.xlsx
+++ b/data/S1986_87_FINAL.xlsx
@@ -60026,7 +60026,7 @@
         <v>127</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>

--- a/data/S1986_87_FINAL.xlsx
+++ b/data/S1986_87_FINAL.xlsx
@@ -23022,7 +23022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L131"/>
+  <dimension ref="A1:N131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23084,6 +23084,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1986_87_FINAL.xlsx
+++ b/data/S1986_87_FINAL.xlsx
@@ -23368,6 +23368,16 @@
           <t>NODE_S1986_87_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0008</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0014</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23382,6 +23392,14 @@
         <is>
           <t>NODE_S1985_86_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -23462,6 +23480,12 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0009</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23476,6 +23500,14 @@
         <is>
           <t>NODE_S1985_86_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>horní polovina ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -23509,6 +23541,16 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0013</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0012</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23523,6 +23565,14 @@
         <is>
           <t>NODE_S1985_86_0009</t>
         </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -23556,6 +23606,8 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23570,6 +23622,14 @@
         <is>
           <t>NODE_S1985_86_0010</t>
         </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="12">
@@ -23603,6 +23663,8 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23617,6 +23679,14 @@
         <is>
           <t>NODE_S1985_86_0011</t>
         </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -23650,6 +23720,8 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23664,6 +23736,14 @@
         <is>
           <t>NODE_S1985_86_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -23697,6 +23777,8 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23711,6 +23793,14 @@
         <is>
           <t>NODE_S1985_86_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="15">
@@ -23744,6 +23834,8 @@
           <t>NODE_S1986_87_0001</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23758,6 +23850,14 @@
         <is>
           <t>NODE_S1985_86_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -23791,6 +23891,8 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23800,6 +23902,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="17">
@@ -23833,6 +23943,16 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0017</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0021</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23842,6 +23962,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -23875,6 +24003,16 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0018</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0020</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23884,6 +24022,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>1.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -23917,6 +24063,16 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0019</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0126</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23926,6 +24082,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>vítězové ČF</t>
+        </is>
+      </c>
+      <c r="N19" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -23959,6 +24123,8 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23968,6 +24134,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N20" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="21">
@@ -24001,6 +24175,8 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24010,6 +24186,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="22">
@@ -24043,6 +24227,8 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24052,6 +24238,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>9.–12. ZČ</t>
+        </is>
+      </c>
+      <c r="N22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -24436,6 +24630,8 @@
           <t>NODE_S1986_87_0027</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24445,6 +24641,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -24525,6 +24729,8 @@
           <t>NODE_S1986_87_0027</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24539,6 +24745,14 @@
         <is>
           <t>NODE_S1985_86_0025</t>
         </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N33" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="34">
@@ -24760,6 +24974,8 @@
           <t>NODE_S1986_87_0033</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24774,6 +24990,14 @@
         <is>
           <t>NODE_S1985_86_0030</t>
         </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N38" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="39">
@@ -24948,6 +25172,8 @@
           <t>NODE_S1986_87_0039</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24962,6 +25188,14 @@
         <is>
           <t>NODE_S1985_86_0034</t>
         </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N42" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="43">
@@ -24995,6 +25229,8 @@
           <t>NODE_S1986_87_0039</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25009,6 +25245,14 @@
         <is>
           <t>NODE_S1985_86_0035</t>
         </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -25042,6 +25286,8 @@
           <t>NODE_S1986_87_0040</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25056,6 +25302,14 @@
         <is>
           <t>NODE_S1985_86_0036</t>
         </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N44" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="45">
@@ -25089,6 +25343,8 @@
           <t>NODE_S1986_87_0040</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25103,6 +25359,14 @@
         <is>
           <t>NODE_S1985_86_0037</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="46">
@@ -25136,6 +25400,8 @@
           <t>NODE_S1986_87_0038</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25155,6 +25421,14 @@
         <is>
           <t>NODE_S1985_86_0038</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -25183,6 +25457,12 @@
           <t>REG_STC</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0051</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25202,6 +25482,14 @@
         <is>
           <t>NODE_S1985_86_0039</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -25413,6 +25701,8 @@
           <t>NODE_S1986_87_0046</t>
         </is>
       </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25422,6 +25712,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="53">
@@ -25779,6 +26077,12 @@
           <t>NODE_S1986_87_0057</t>
         </is>
       </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0060</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25793,6 +26097,14 @@
         <is>
           <t>NODE_S1985_86_0053</t>
         </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -25826,6 +26138,8 @@
           <t>NODE_S1986_87_0057</t>
         </is>
       </c>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25840,6 +26154,14 @@
         <is>
           <t>NODE_S1985_86_0054</t>
         </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N61" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="62">
@@ -26019,6 +26341,16 @@
           <t>NODE_S1986_87_0062</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0065</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0066</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26028,6 +26360,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -26061,6 +26401,8 @@
           <t>NODE_S1986_87_0062</t>
         </is>
       </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26070,6 +26412,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="67">
@@ -26103,6 +26453,8 @@
           <t>NODE_S1986_87_0062</t>
         </is>
       </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26112,6 +26464,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -26286,6 +26646,8 @@
           <t>NODE_S1986_87_0062</t>
         </is>
       </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26295,6 +26657,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N71" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="72">
@@ -26474,6 +26844,16 @@
           <t>NODE_S1986_87_0072</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0075</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0076</t>
+        </is>
+      </c>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26483,6 +26863,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -26516,6 +26904,8 @@
           <t>NODE_S1986_87_0072</t>
         </is>
       </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26525,6 +26915,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N76" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="77">
@@ -26558,6 +26956,8 @@
           <t>NODE_S1986_87_0072</t>
         </is>
       </c>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26567,6 +26967,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>7.–10. ZČ</t>
+        </is>
+      </c>
+      <c r="N77" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="78">
@@ -26788,6 +27196,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26797,6 +27207,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -26830,6 +27248,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26839,6 +27259,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="84">
@@ -26872,6 +27300,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26881,6 +27311,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="85">
@@ -26914,6 +27352,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26923,6 +27363,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="86">
@@ -26956,6 +27404,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26965,6 +27415,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N86" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="87">
@@ -26998,6 +27456,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27007,6 +27467,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>o 11. místo</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -27040,6 +27508,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27049,6 +27519,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -27082,6 +27560,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27091,6 +27571,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N89" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="90">
@@ -27124,6 +27612,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27133,6 +27623,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N90" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="91">
@@ -27166,6 +27664,8 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27175,6 +27675,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>o 9. místo</t>
+        </is>
+      </c>
+      <c r="N91" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -27784,6 +28292,8 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27793,6 +28303,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="106">
@@ -27826,6 +28344,8 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27835,6 +28355,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N106" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -27868,6 +28396,8 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27877,6 +28407,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N107" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="108">
@@ -27910,6 +28448,8 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27919,6 +28459,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N108" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="109">
@@ -27952,6 +28500,8 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27961,6 +28511,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N109" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="110">
@@ -27994,6 +28552,8 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28003,6 +28563,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N110" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -28177,6 +28745,12 @@
           <t>NODE_S1986_87_0111</t>
         </is>
       </c>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0115</t>
+        </is>
+      </c>
       <c r="I114" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28191,6 +28765,14 @@
         <is>
           <t>NODE_S1985_86_0084</t>
         </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N114" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="115">
@@ -28266,6 +28848,8 @@
           <t>NODE_S1986_87_0111</t>
         </is>
       </c>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28280,6 +28864,14 @@
         <is>
           <t>NODE_S1985_86_0086</t>
         </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N116" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -28679,6 +29271,12 @@
           <t>NODE_S1986_87_0129</t>
         </is>
       </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>NODE_S1986_87_0125</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28688,6 +29286,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N125" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -28721,6 +29327,8 @@
           <t>NODE_S1986_87_0129</t>
         </is>
       </c>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28730,6 +29338,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N126" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="127">
@@ -28763,6 +29379,8 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28772,6 +29390,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>poražení SF</t>
+        </is>
+      </c>
+      <c r="N127" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="128">
@@ -28931,6 +29557,8 @@
           <t>NODE_S1986_87_0129</t>
         </is>
       </c>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28940,6 +29568,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>poražení ČF</t>
+        </is>
+      </c>
+      <c r="N131" t="n">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/data/S1986_87_FINAL.xlsx
+++ b/data/S1986_87_FINAL.xlsx
@@ -719,6 +719,11 @@
           <t>Tesla Pardubice</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>34</v>
       </c>
@@ -23485,7 +23490,6 @@
           <t>NODE_S1986_87_0009</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23606,8 +23610,6 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23663,8 +23665,6 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23720,8 +23720,6 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23777,8 +23775,6 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23834,8 +23830,6 @@
           <t>NODE_S1986_87_0001</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -23891,8 +23885,6 @@
           <t>NODE_S1986_87_0007</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24123,8 +24115,6 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24175,8 +24165,6 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24227,8 +24215,6 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24630,8 +24616,6 @@
           <t>NODE_S1986_87_0027</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24729,8 +24713,6 @@
           <t>NODE_S1986_87_0027</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -24974,8 +24956,6 @@
           <t>NODE_S1986_87_0033</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25172,8 +25152,6 @@
           <t>NODE_S1986_87_0039</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25229,8 +25207,6 @@
           <t>NODE_S1986_87_0039</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25286,8 +25262,6 @@
           <t>NODE_S1986_87_0040</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25343,8 +25317,6 @@
           <t>NODE_S1986_87_0040</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25400,8 +25372,6 @@
           <t>NODE_S1986_87_0038</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25462,7 +25432,6 @@
           <t>NODE_S1986_87_0051</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -25701,8 +25670,6 @@
           <t>NODE_S1986_87_0046</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26082,7 +26049,6 @@
           <t>NODE_S1986_87_0060</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26138,8 +26104,6 @@
           <t>NODE_S1986_87_0057</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26401,8 +26365,6 @@
           <t>NODE_S1986_87_0062</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26453,8 +26415,6 @@
           <t>NODE_S1986_87_0062</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26646,8 +26606,6 @@
           <t>NODE_S1986_87_0062</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26904,8 +26862,6 @@
           <t>NODE_S1986_87_0072</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -26956,8 +26912,6 @@
           <t>NODE_S1986_87_0072</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27196,8 +27150,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27248,8 +27200,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27300,8 +27250,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27352,8 +27300,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27404,8 +27350,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27456,8 +27400,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27508,8 +27450,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27560,8 +27500,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27612,8 +27550,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -27664,8 +27600,6 @@
           <t>NODE_S1986_87_0078</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28292,8 +28226,6 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28344,8 +28276,6 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr"/>
-      <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28396,8 +28326,6 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr"/>
-      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28448,8 +28376,6 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr"/>
-      <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28500,8 +28426,6 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28552,8 +28476,6 @@
           <t>NODE_S1986_87_0092</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr"/>
-      <c r="H110" t="inlineStr"/>
       <c r="I110" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -28745,7 +28667,6 @@
           <t>NODE_S1986_87_0111</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
           <t>NODE_S1986_87_0115</t>
@@ -28848,8 +28769,6 @@
           <t>NODE_S1986_87_0111</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29276,7 +29195,6 @@
           <t>NODE_S1986_87_0125</t>
         </is>
       </c>
-      <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29327,8 +29245,6 @@
           <t>NODE_S1986_87_0129</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr"/>
-      <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29379,8 +29295,6 @@
           <t>NODE_S1986_87_0004</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr"/>
-      <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -29557,8 +29471,6 @@
           <t>NODE_S1986_87_0129</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr"/>
-      <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -58640,7 +58552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58844,6 +58756,18 @@
       <c r="B17" t="inlineStr">
         <is>
           <t>II.SNHL finále: první utkání doma; do kvalifikace o 2. SNHL sestoupila Levoča; TJ Spartak BEZ Bratislava přímo do KP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Tesla Pardubice</t>
         </is>
       </c>
     </row>
